--- a/data/trans_orig/P05A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P05A_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>130104</t>
+          <t>131958</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>172098</t>
+          <t>170858</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85332</t>
+          <t>87470</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118762</t>
+          <t>118210</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>227581</t>
+          <t>226518</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>280539</t>
+          <t>280477</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,94%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301678</t>
+          <t>302918</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>343672</t>
+          <t>341818</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>187918</t>
+          <t>188470</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>221348</t>
+          <t>219210</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>499918</t>
+          <t>499980</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>552876</t>
+          <t>553939</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,98%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>97137</t>
+          <t>97927</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>134895</t>
+          <t>134220</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95347</t>
+          <t>94104</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>128890</t>
+          <t>128699</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201812</t>
+          <t>202087</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>253306</t>
+          <t>254456</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>232039</t>
+          <t>232714</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>269797</t>
+          <t>269007</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>242975</t>
+          <t>243166</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>276518</t>
+          <t>277761</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>485493</t>
+          <t>484343</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>536987</t>
+          <t>536712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,65%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>139692</t>
+          <t>137445</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>183059</t>
+          <t>181783</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50966</t>
+          <t>50959</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75638</t>
+          <t>75192</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>198215</t>
+          <t>201432</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>249258</t>
+          <t>248621</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>359330</t>
+          <t>360606</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>402697</t>
+          <t>404944</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92144</t>
+          <t>92590</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116816</t>
+          <t>116823</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>460913</t>
+          <t>461550</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>511956</t>
+          <t>508739</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,64%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>325565</t>
+          <t>330318</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>392320</t>
+          <t>396819</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>227473</t>
+          <t>228992</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>277832</t>
+          <t>278255</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>573926</t>
+          <t>569646</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>651618</t>
+          <t>651897</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>846014</t>
+          <t>841515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>912769</t>
+          <t>908016</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>436453</t>
+          <t>436030</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>486812</t>
+          <t>485293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1301002</t>
+          <t>1300723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1378694</t>
+          <t>1382974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94915</t>
+          <t>94135</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>130036</t>
+          <t>130440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>194803</t>
+          <t>195547</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>243792</t>
+          <t>242477</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>299985</t>
+          <t>301029</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>360822</t>
+          <t>360781</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>220519</t>
+          <t>220115</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>255640</t>
+          <t>256420</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>324960</t>
+          <t>326275</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>373949</t>
+          <t>373205</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>558485</t>
+          <t>558526</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>619322</t>
+          <t>618278</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,25%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56435</t>
+          <t>54848</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86507</t>
+          <t>83930</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>382050</t>
+          <t>381270</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>445234</t>
+          <t>447111</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>445958</t>
+          <t>448083</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>517398</t>
+          <t>519853</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,6%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>211694</t>
+          <t>214271</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>241766</t>
+          <t>243353</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>803526</t>
+          <t>801649</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>866710</t>
+          <t>867490</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1029562</t>
+          <t>1027107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1101002</t>
+          <t>1098877</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,03%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>914017</t>
+          <t>910438</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1019596</t>
+          <t>1018503</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1106510</t>
+          <t>1108080</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1217764</t>
+          <t>1215029</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2053585</t>
+          <t>2053073</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2206947</t>
+          <t>2199471</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2250594</t>
+          <t>2251687</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2356173</t>
+          <t>2359752</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2160360</t>
+          <t>2163095</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2271614</t>
+          <t>2270044</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4441367</t>
+          <t>4448843</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4594729</t>
+          <t>4595241</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,12%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>173359</t>
+          <t>176335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>216521</t>
+          <t>219390</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>117875</t>
+          <t>116117</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>154608</t>
+          <t>152997</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>305778</t>
+          <t>303425</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>360806</t>
+          <t>360850</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,01%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>220690</t>
+          <t>217821</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>263852</t>
+          <t>260876</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>159846</t>
+          <t>161457</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>196579</t>
+          <t>198337</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>390859</t>
+          <t>390815</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>445887</t>
+          <t>448240</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,63%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>146844</t>
+          <t>146153</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>190413</t>
+          <t>190323</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122278</t>
+          <t>123131</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>159813</t>
+          <t>160305</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>281022</t>
+          <t>279076</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>336698</t>
+          <t>339010</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>228384</t>
+          <t>228474</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>271953</t>
+          <t>272644</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>176479</t>
+          <t>175987</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>214014</t>
+          <t>213161</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>418391</t>
+          <t>416079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>474067</t>
+          <t>476013</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>63,04%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>235721</t>
+          <t>234152</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>283597</t>
+          <t>284966</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88555</t>
+          <t>88026</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119462</t>
+          <t>121482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>332039</t>
+          <t>334009</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>390772</t>
+          <t>395459</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,58%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>344275</t>
+          <t>342906</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>392151</t>
+          <t>393720</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139654</t>
+          <t>137634</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>170561</t>
+          <t>171090</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>496216</t>
+          <t>491529</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>554949</t>
+          <t>552979</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,34%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>431098</t>
+          <t>427943</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>499740</t>
+          <t>498044</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>276407</t>
+          <t>278557</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>332690</t>
+          <t>334633</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>720047</t>
+          <t>724541</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>809479</t>
+          <t>814342</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,4%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>655399</t>
+          <t>657095</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>724041</t>
+          <t>727196</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>432907</t>
+          <t>430964</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>489190</t>
+          <t>487040</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1111256</t>
+          <t>1106393</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1200688</t>
+          <t>1196194</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,28%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>152512</t>
+          <t>153238</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>195952</t>
+          <t>196231</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>248196</t>
+          <t>249649</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>303675</t>
+          <t>301711</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>416530</t>
+          <t>415766</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>488576</t>
+          <t>483349</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>314644</t>
+          <t>314365</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>358084</t>
+          <t>357358</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>456891</t>
+          <t>458855</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>512370</t>
+          <t>510917</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>782586</t>
+          <t>787813</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>854632</t>
+          <t>855396</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,29%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81576</t>
+          <t>80659</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>111857</t>
+          <t>112251</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>420589</t>
+          <t>424776</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>485025</t>
+          <t>490610</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>514522</t>
+          <t>512901</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>593314</t>
+          <t>589461</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,87%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155025</t>
+          <t>154631</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>185306</t>
+          <t>186223</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>623225</t>
+          <t>617640</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>687661</t>
+          <t>683474</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>781818</t>
+          <t>785671</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>860610</t>
+          <t>862231</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,7%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1303956</t>
+          <t>1302571</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1423479</t>
+          <t>1420676</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1354929</t>
+          <t>1355963</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1476207</t>
+          <t>1475550</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2690695</t>
+          <t>2678523</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2860182</t>
+          <t>2855471</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1993017</t>
+          <t>1995820</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2112540</t>
+          <t>2113925</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2068067</t>
+          <t>2068724</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2189345</t>
+          <t>2188311</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4100588</t>
+          <t>4105299</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4270075</t>
+          <t>4282247</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,52%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>146310</t>
+          <t>144573</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>188720</t>
+          <t>186751</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>123190</t>
+          <t>125489</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>160585</t>
+          <t>162002</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>280734</t>
+          <t>279290</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>338029</t>
+          <t>337713</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,51%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>240372</t>
+          <t>242341</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>282782</t>
+          <t>284519</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>186470</t>
+          <t>185053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>223865</t>
+          <t>221566</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>438118</t>
+          <t>438434</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>495413</t>
+          <t>496857</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,02%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>119521</t>
+          <t>119815</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>157596</t>
+          <t>157023</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>123838</t>
+          <t>125636</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>162716</t>
+          <t>162815</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>257321</t>
+          <t>256971</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>311007</t>
+          <t>309144</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,25%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>219631</t>
+          <t>220204</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>257706</t>
+          <t>257412</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>209557</t>
+          <t>209458</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>248435</t>
+          <t>246637</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>438493</t>
+          <t>440356</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>492179</t>
+          <t>492529</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,71%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>166420</t>
+          <t>166634</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>212087</t>
+          <t>210240</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46791</t>
+          <t>46510</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72351</t>
+          <t>72577</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>223063</t>
+          <t>219665</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>273178</t>
+          <t>273904</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,81%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309827</t>
+          <t>311674</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>355494</t>
+          <t>355280</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93772</t>
+          <t>93546</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119332</t>
+          <t>119613</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>414858</t>
+          <t>414132</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>464973</t>
+          <t>468371</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>68,07%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>380383</t>
+          <t>382452</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>445286</t>
+          <t>446601</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>279366</t>
+          <t>281084</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>336391</t>
+          <t>335703</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>673206</t>
+          <t>674504</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>762608</t>
+          <t>761418</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>704352</t>
+          <t>703037</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>769255</t>
+          <t>767186</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>489485</t>
+          <t>490173</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>546510</t>
+          <t>544792</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1212906</t>
+          <t>1214096</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1302308</t>
+          <t>1301010</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,86%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>193135</t>
+          <t>190822</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>239471</t>
+          <t>239644</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>244699</t>
+          <t>244512</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>295933</t>
+          <t>295452</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>448286</t>
+          <t>447337</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>522688</t>
+          <t>519852</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>381235</t>
+          <t>381062</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>427571</t>
+          <t>429884</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>441276</t>
+          <t>441757</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>492510</t>
+          <t>492697</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>835227</t>
+          <t>838063</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>909629</t>
+          <t>910578</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,06%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82473</t>
+          <t>83260</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>114935</t>
+          <t>115756</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>341066</t>
+          <t>342662</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>407932</t>
+          <t>406954</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>438072</t>
+          <t>433781</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>510846</t>
+          <t>507469</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170943</t>
+          <t>170122</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>203405</t>
+          <t>202618</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>672822</t>
+          <t>673800</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>739688</t>
+          <t>738092</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>855785</t>
+          <t>859162</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>928559</t>
+          <t>932850</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1159535</t>
+          <t>1159693</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1269790</t>
+          <t>1274501</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1238121</t>
+          <t>1234924</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1355221</t>
+          <t>1354000</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2422132</t>
+          <t>2420761</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2594163</t>
+          <t>2585558</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2114665</t>
+          <t>2109954</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2224920</t>
+          <t>2224762</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2174069</t>
+          <t>2175290</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2291169</t>
+          <t>2294366</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4319581</t>
+          <t>4328186</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4491612</t>
+          <t>4492983</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,99%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>118747</t>
+          <t>127513</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99578</t>
+          <t>107428</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>140666</t>
+          <t>150346</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>107095</t>
+          <t>118930</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92209</t>
+          <t>103103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>123968</t>
+          <t>137190</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>225843</t>
+          <t>246443</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>201066</t>
+          <t>221215</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>257769</t>
+          <t>279621</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,95%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>386465</t>
+          <t>423105</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>364546</t>
+          <t>400272</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>405634</t>
+          <t>443190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>339030</t>
+          <t>368049</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>322157</t>
+          <t>349789</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>353916</t>
+          <t>383876</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>725494</t>
+          <t>791154</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>693568</t>
+          <t>757976</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750271</t>
+          <t>816382</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,68%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>951337</t>
+          <t>1037597</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>951337</t>
+          <t>1037597</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>951337</t>
+          <t>1037597</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77622</t>
+          <t>82031</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62994</t>
+          <t>68232</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95952</t>
+          <t>102840</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>95217</t>
+          <t>103463</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81742</t>
+          <t>88127</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111754</t>
+          <t>118811</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172839</t>
+          <t>185495</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153185</t>
+          <t>164516</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>197535</t>
+          <t>212145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>374591</t>
+          <t>401181</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356261</t>
+          <t>380372</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>389219</t>
+          <t>414980</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>287363</t>
+          <t>319680</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>270826</t>
+          <t>304332</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>300838</t>
+          <t>335016</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>661954</t>
+          <t>720860</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>637258</t>
+          <t>694210</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>681608</t>
+          <t>741839</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,85%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>91670</t>
+          <t>99173</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32848</t>
+          <t>81976</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153886</t>
+          <t>120208</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33646</t>
+          <t>37985</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25169</t>
+          <t>29152</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41981</t>
+          <t>47345</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>125316</t>
+          <t>137158</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58824</t>
+          <t>116706</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>186312</t>
+          <t>159746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>576594</t>
+          <t>372439</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>514378</t>
+          <t>351404</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>635416</t>
+          <t>389636</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>133265</t>
+          <t>149512</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>124930</t>
+          <t>140152</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141742</t>
+          <t>158345</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>709859</t>
+          <t>521951</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>648863</t>
+          <t>499363</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>776351</t>
+          <t>542403</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>82,29%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>164749</t>
+          <t>181880</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>138789</t>
+          <t>158467</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>196381</t>
+          <t>213106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>361621</t>
+          <t>181092</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>188272</t>
+          <t>159411</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>604770</t>
+          <t>202031</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>526370</t>
+          <t>362972</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>346774</t>
+          <t>330966</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1047761</t>
+          <t>400517</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>869906</t>
+          <t>948845</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>838274</t>
+          <t>917619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>895866</t>
+          <t>972258</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>616473</t>
+          <t>680119</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>373324</t>
+          <t>659180</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>789822</t>
+          <t>701800</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1486379</t>
+          <t>1628965</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>964988</t>
+          <t>1591420</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1665975</t>
+          <t>1660971</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>83,38%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034655</t>
+          <t>1130725</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034655</t>
+          <t>1130725</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034655</t>
+          <t>1130725</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012749</t>
+          <t>1991937</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012749</t>
+          <t>1991937</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012749</t>
+          <t>1991937</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>86197</t>
+          <t>105435</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69463</t>
+          <t>87066</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>125577</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>139056</t>
+          <t>166545</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>104541</t>
+          <t>148303</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>163445</t>
+          <t>187033</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>225252</t>
+          <t>271981</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>186011</t>
+          <t>244941</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>256873</t>
+          <t>300716</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>388849</t>
+          <t>462529</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>369350</t>
+          <t>442387</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>405583</t>
+          <t>480898</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>702279</t>
+          <t>664305</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>677890</t>
+          <t>643817</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>736794</t>
+          <t>682547</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1091129</t>
+          <t>1126833</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1059508</t>
+          <t>1098098</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1130370</t>
+          <t>1153873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>82,49%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>39938</t>
+          <t>41482</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22508</t>
+          <t>24438</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63639</t>
+          <t>63828</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>109368</t>
+          <t>122211</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>91804</t>
+          <t>104575</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>129333</t>
+          <t>144379</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>149306</t>
+          <t>163693</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>123043</t>
+          <t>137598</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>177402</t>
+          <t>195203</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>200569</t>
+          <t>195746</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>176868</t>
+          <t>173400</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>217999</t>
+          <t>212790</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>652003</t>
+          <t>722070</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>632038</t>
+          <t>699902</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>669567</t>
+          <t>739706</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>852572</t>
+          <t>917816</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>824476</t>
+          <t>886306</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>878835</t>
+          <t>943911</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,28%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>578924</t>
+          <t>637515</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>444486</t>
+          <t>588895</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>646860</t>
+          <t>695007</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>846002</t>
+          <t>730227</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>664562</t>
+          <t>684886</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1294259</t>
+          <t>776359</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1424925</t>
+          <t>1367742</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1208312</t>
+          <t>1304909</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1961601</t>
+          <t>1442309</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2796973</t>
+          <t>2803843</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2729037</t>
+          <t>2746351</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2931411</t>
+          <t>2852463</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2730413</t>
+          <t>2903735</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2282156</t>
+          <t>2857603</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2911853</t>
+          <t>2949076</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5527387</t>
+          <t>5707578</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4990711</t>
+          <t>5633011</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5744000</t>
+          <t>5770411</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3375897</t>
+          <t>3441358</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3375897</t>
+          <t>3441358</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3375897</t>
+          <t>3441358</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3576415</t>
+          <t>3633962</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3576415</t>
+          <t>3633962</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3576415</t>
+          <t>3633962</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6952312</t>
+          <t>7075320</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6952312</t>
+          <t>7075320</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6952312</t>
+          <t>7075320</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
